--- a/saida_skus/SKU_UTD-036-ORGANIZADOR-GIRATORIO-BAMBU-FRUTEIRA.xlsx
+++ b/saida_skus/SKU_UTD-036-ORGANIZADOR-GIRATORIO-BAMBU-FRUTEIRA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -545,14 +545,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-036</t>
@@ -575,7 +575,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -583,10 +583,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -595,39 +593,37 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -699,12 +695,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -776,12 +772,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -853,12 +849,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -930,12 +926,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1007,12 +1003,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1084,12 +1080,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1161,12 +1157,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1238,12 +1234,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1315,12 +1311,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1392,12 +1388,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1469,12 +1465,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1546,12 +1542,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1623,12 +1619,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1700,12 +1696,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1777,12 +1773,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1854,12 +1850,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1931,12 +1927,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2008,12 +2004,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2085,12 +2081,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2162,12 +2158,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2239,12 +2235,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2316,12 +2312,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2393,12 +2389,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2470,12 +2466,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2547,12 +2543,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2624,12 +2620,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2701,12 +2697,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2778,12 +2774,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2855,12 +2851,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2932,12 +2928,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3009,12 +3005,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3086,12 +3082,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3163,12 +3159,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3240,12 +3236,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3317,12 +3313,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3394,12 +3390,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3471,12 +3467,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3548,12 +3544,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3625,12 +3621,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3702,12 +3698,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3779,12 +3775,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3856,12 +3852,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3933,12 +3929,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4010,12 +4006,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4087,12 +4083,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4164,12 +4160,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4241,12 +4237,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4318,12 +4314,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4395,12 +4391,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4472,12 +4468,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4549,12 +4545,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4626,12 +4622,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4703,12 +4699,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4780,12 +4776,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4857,12 +4853,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4934,12 +4930,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5011,12 +5007,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5088,12 +5084,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5165,12 +5161,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5242,12 +5238,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5319,12 +5315,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5396,12 +5392,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5473,12 +5469,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5550,12 +5546,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5627,12 +5623,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5704,12 +5700,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5781,12 +5777,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5858,12 +5854,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5935,12 +5931,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6012,12 +6008,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6089,12 +6085,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6166,12 +6162,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6243,12 +6239,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6320,12 +6316,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6397,12 +6393,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6474,12 +6470,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6551,12 +6547,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6628,12 +6624,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6705,12 +6701,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6782,12 +6778,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6859,12 +6855,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6936,82 +6932,159 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-036</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Organizador Giratório Bambu fruteira</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>7006602056</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-036-ORGANIZADOR-GIRATORIO-BAMBU-FRUTEIRA.xlsx
+++ b/saida_skus/SKU_UTD-036-ORGANIZADOR-GIRATORIO-BAMBU-FRUTEIRA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -72,12 +76,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -445,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -545,14 +552,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-036</t>
@@ -575,7 +582,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 65,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -584,24 +591,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -618,14 +625,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-036</t>
@@ -648,7 +655,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -656,10 +663,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -668,39 +673,37 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -772,12 +775,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -849,12 +852,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -926,12 +929,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1003,12 +1006,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1080,12 +1083,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1157,12 +1160,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1234,12 +1237,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1311,12 +1314,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1388,12 +1391,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1465,12 +1468,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1542,12 +1545,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1619,12 +1622,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1696,12 +1699,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1773,12 +1776,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1850,12 +1853,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1927,12 +1930,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2004,12 +2007,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2081,12 +2084,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2158,12 +2161,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2235,12 +2238,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2312,12 +2315,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2389,12 +2392,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2466,12 +2469,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2543,12 +2546,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2620,12 +2623,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2697,12 +2700,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2774,12 +2777,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2851,12 +2854,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2928,12 +2931,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3005,12 +3008,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3082,12 +3085,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3159,12 +3162,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3236,12 +3239,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3313,12 +3316,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3390,12 +3393,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3467,12 +3470,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3544,12 +3547,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3621,12 +3624,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3698,12 +3701,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3775,12 +3778,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3852,12 +3855,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3929,12 +3932,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4006,12 +4009,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4083,12 +4086,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4160,12 +4163,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4237,12 +4240,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4314,12 +4317,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4391,12 +4394,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4468,12 +4471,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4545,12 +4548,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4622,12 +4625,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4699,12 +4702,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4776,12 +4779,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4853,12 +4856,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4930,12 +4933,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5007,12 +5010,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5084,12 +5087,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5161,12 +5164,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5238,12 +5241,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5315,12 +5318,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5392,12 +5395,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5469,12 +5472,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5546,12 +5549,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5623,12 +5626,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5700,12 +5703,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5777,12 +5780,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5854,12 +5857,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5931,12 +5934,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6008,12 +6011,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6085,12 +6088,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6162,12 +6165,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6239,12 +6242,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6316,12 +6319,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6393,12 +6396,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6470,12 +6473,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6547,12 +6550,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6624,12 +6627,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6701,12 +6704,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6778,12 +6781,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6855,12 +6858,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6932,12 +6935,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -7009,82 +7012,159 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>UTD-036</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Organizador Giratório Bambu fruteira</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>7006602056</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O86"/>
+  <autoFilter ref="A1:O87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-036-ORGANIZADOR-GIRATORIO-BAMBU-FRUTEIRA.xlsx
+++ b/saida_skus/SKU_UTD-036-ORGANIZADOR-GIRATORIO-BAMBU-FRUTEIRA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,10 @@
     <font>
       <b val="1"/>
       <color rgb="00D93025"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,6 +89,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -452,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-036</t>
@@ -582,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -625,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-036</t>
@@ -655,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 65,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -664,24 +671,24 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -698,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-036</t>
@@ -728,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -736,10 +743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -748,39 +753,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -852,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -929,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1006,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1083,12 +1086,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1160,12 +1163,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1237,12 +1240,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1314,12 +1317,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1391,12 +1394,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1468,12 +1471,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1545,12 +1548,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1622,12 +1625,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1699,12 +1702,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1776,12 +1779,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1853,12 +1856,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1930,12 +1933,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2007,12 +2010,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2084,12 +2087,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2161,12 +2164,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2238,12 +2241,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2315,12 +2318,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2392,12 +2395,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2469,12 +2472,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2546,12 +2549,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2623,12 +2626,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2700,12 +2703,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2777,12 +2780,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2854,12 +2857,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2931,12 +2934,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3008,12 +3011,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3085,12 +3088,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3162,12 +3165,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3239,12 +3242,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3316,12 +3319,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3393,12 +3396,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3470,12 +3473,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3547,12 +3550,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3624,12 +3627,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3701,12 +3704,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3778,12 +3781,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3855,12 +3858,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3932,12 +3935,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4009,12 +4012,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4086,12 +4089,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4163,12 +4166,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4240,12 +4243,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4317,12 +4320,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4394,12 +4397,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4471,12 +4474,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4548,12 +4551,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4625,12 +4628,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4702,12 +4705,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4779,12 +4782,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4856,12 +4859,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4933,12 +4936,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5010,12 +5013,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5087,12 +5090,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5164,12 +5167,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5241,12 +5244,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5318,12 +5321,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5395,12 +5398,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5472,12 +5475,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5549,12 +5552,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5626,12 +5629,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5703,12 +5706,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5780,12 +5783,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5857,12 +5860,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5934,12 +5937,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6011,12 +6014,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6088,12 +6091,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6165,12 +6168,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6242,12 +6245,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6319,12 +6322,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6396,12 +6399,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6473,12 +6476,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6550,12 +6553,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6627,12 +6630,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6704,12 +6707,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6781,12 +6784,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6858,12 +6861,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6935,12 +6938,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -7012,12 +7015,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7089,82 +7092,159 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>UTD-036</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Organizador Giratório Bambu fruteira</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>7006602056</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O87"/>
+  <autoFilter ref="A1:O88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-036-ORGANIZADOR-GIRATORIO-BAMBU-FRUTEIRA.xlsx
+++ b/saida_skus/SKU_UTD-036-ORGANIZADOR-GIRATORIO-BAMBU-FRUTEIRA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O88"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 259,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,8%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>58</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 262,5%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 129,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 98,5%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 65,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 733,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,51 +816,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,59 +881,55 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 65,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -970,51 +962,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1047,10 +1035,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1059,39 +1045,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1163,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1240,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1317,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1394,12 +1378,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1471,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1548,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1625,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1702,12 +1686,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1779,12 +1763,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1856,12 +1840,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1933,12 +1917,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2010,12 +1994,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2087,12 +2071,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2164,12 +2148,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2241,12 +2225,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2318,12 +2302,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2395,12 +2379,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2472,12 +2456,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2549,12 +2533,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2626,12 +2610,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2703,12 +2687,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2780,12 +2764,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2857,12 +2841,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2934,12 +2918,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3011,12 +2995,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3088,12 +3072,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3165,12 +3149,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3242,12 +3226,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3319,12 +3303,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3396,12 +3380,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3473,12 +3457,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3550,12 +3534,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3627,12 +3611,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3704,12 +3688,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3781,12 +3765,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3858,12 +3842,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3935,12 +3919,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4012,12 +3996,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4089,12 +4073,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4166,12 +4150,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4243,12 +4227,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4320,12 +4304,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4397,12 +4381,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4474,12 +4458,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4551,12 +4535,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4628,12 +4612,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4705,12 +4689,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4782,12 +4766,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4859,12 +4843,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4936,12 +4920,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5013,12 +4997,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5090,12 +5074,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5167,12 +5151,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5244,12 +5228,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5321,12 +5305,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5398,12 +5382,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5475,12 +5459,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5552,12 +5536,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5629,12 +5613,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5706,12 +5690,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5783,12 +5767,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5860,12 +5844,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5937,12 +5921,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6014,12 +5998,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6091,12 +6075,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6168,12 +6152,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6245,12 +6229,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6322,12 +6306,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6399,12 +6383,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6476,12 +6460,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6553,12 +6537,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6630,12 +6614,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6707,12 +6691,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6784,12 +6768,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6861,12 +6845,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6938,12 +6922,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -7015,12 +6999,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7092,12 +7076,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7169,82 +7153,390 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>UTD-036</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Organizador Giratório Bambu fruteira</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>7006602056</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>R$ 78,90</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-036</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Organizador Giratório Bambu fruteira</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>7006602056</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O88"/>
+  <autoFilter ref="A1:O92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>